--- a/tools/myCustomBlockly/製作積木教學/產生積木程式碼_StepMotor.xlsx
+++ b/tools/myCustomBlockly/製作積木教學/產生積木程式碼_StepMotor.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ArduinoSample\tools\myCustomBlockly\製作積木教學\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\myCustomBlockly\製作積木教學\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D663616-7010-48E4-9726-071833E40F0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9135" tabRatio="732" activeTab="4"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" tabRatio="732" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="變數" sheetId="5" r:id="rId1"/>
@@ -23,22 +24,31 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">LOOP!$C$1:$D$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">SETUP!$A$2:$J$3</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>AMANI</author>
   </authors>
   <commentList>
-    <comment ref="D2" authorId="0" shapeId="0">
+    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -58,12 +68,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>AMANI</author>
   </authors>
   <commentList>
-    <comment ref="D2" authorId="0" shapeId="0">
+    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -83,12 +93,12 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>AMANI</author>
   </authors>
   <commentList>
-    <comment ref="C2" authorId="0" shapeId="0">
+    <comment ref="C2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
       <text>
         <r>
           <rPr>
@@ -861,7 +871,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="20">
     <font>
       <sz val="12"/>
@@ -1432,7 +1442,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -1483,7 +1493,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R11"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -1649,7 +1659,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -1835,11 +1845,12 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="64.25" customWidth="1"/>
+    <col min="2" max="2" width="22.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1944,7 +1955,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L14"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
